--- a/EG2B.xlsx
+++ b/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t/>
   </si>
   <si>
-    <t>20137991</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 700ML</t>
+    <t>20126648</t>
+  </si>
+  <si>
+    <t>LE MINERALE 6X330ML</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -40,13 +40,157 @@
     <t>2</t>
   </si>
   <si>
+    <t>20037153</t>
+  </si>
+  <si>
+    <t>KAKI3 PENYEGAR 500ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
+  </si>
+  <si>
+    <t>20012573</t>
+  </si>
+  <si>
+    <t>FRESTEA TEH MLATI500</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20036765</t>
+  </si>
+  <si>
+    <t>FRESTEA GRN MADU 500</t>
+  </si>
+  <si>
+    <t>20065778</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 390 ML</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20065779</t>
+  </si>
+  <si>
+    <t>SPRITE PET 390 ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20065780</t>
+  </si>
+  <si>
+    <t>FANTA STRW PET 390ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20124899</t>
+  </si>
+  <si>
+    <t>CHI/FRST LYC/FZY 480</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20124898</t>
+  </si>
+  <si>
+    <t>CHI/FRST WHT/PCH 480</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10036647</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU UHT CHO1L</t>
+  </si>
+  <si>
+    <t>10000405</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU UHT PLN1L</t>
+  </si>
+  <si>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
+  </si>
+  <si>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
+  </si>
+  <si>
+    <t>20083795</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT CHO 6X110</t>
+  </si>
+  <si>
+    <t>10000107</t>
+  </si>
+  <si>
+    <t>GREEN SAND ORGNL 330</t>
+  </si>
+  <si>
     <t>20005529</t>
   </si>
   <si>
     <t>NESTLE PURE LIFE 600</t>
   </si>
   <si>
-    <t>3</t>
+    <t>20077499</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6+ BTL600</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>20128233</t>
+  </si>
+  <si>
+    <t>NU CHO TEA HZLTEA330</t>
   </si>
   <si>
     <t>20019674</t>
@@ -55,196 +199,100 @@
     <t>YOU C1000 ORG WTR500</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20019673</t>
   </si>
   <si>
     <t>YOU C1000 LMN WTR500</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20043877</t>
-  </si>
-  <si>
-    <t>FLORIDINA ORANGE 350</t>
-  </si>
-  <si>
-    <t>20113377</t>
-  </si>
-  <si>
-    <t>FLRDINA COCO BIT 350</t>
-  </si>
-  <si>
-    <t>20047245</t>
-  </si>
-  <si>
-    <t>MOGU MOGU CCONUT 320</t>
-  </si>
-  <si>
-    <t>20042848</t>
-  </si>
-  <si>
-    <t>MOGU MOGU LYCHHE 320</t>
-  </si>
-  <si>
-    <t>20076486</t>
-  </si>
-  <si>
-    <t>MOGU MOGU MELON 320</t>
-  </si>
-  <si>
-    <t>20042859</t>
-  </si>
-  <si>
-    <t>MOGU MOGU MANGGA 320</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20048546</t>
-  </si>
-  <si>
-    <t>HEMAVITON C1000 330</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20103368</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LMN 330</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20133709</t>
-  </si>
-  <si>
-    <t>POLARIS SARSAPRLA330</t>
+    <t>20069773</t>
+  </si>
+  <si>
+    <t>ISOPLUS BTL 350ML</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>20138376</t>
+  </si>
+  <si>
+    <t>BEBELAC 1 UHT 105ML</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20138252</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS ULTIMT250</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20107748</t>
-  </si>
-  <si>
-    <t>MILKU SUSU CKLT 200</t>
-  </si>
-  <si>
-    <t>20107749</t>
-  </si>
-  <si>
-    <t>MILKU SUSU STRO 200</t>
-  </si>
-  <si>
-    <t>20083795</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT CHO 6X110</t>
-  </si>
-  <si>
-    <t>20070569</t>
-  </si>
-  <si>
-    <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>20136644</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT MARSM200</t>
-  </si>
-  <si>
-    <t>20091807</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT CKLT 200</t>
-  </si>
-  <si>
-    <t>20137977</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT BBLGM200</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20021571</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VAN 570G</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20033353</t>
-  </si>
-  <si>
-    <t>HILO/S HI-CAL CHO250</t>
-  </si>
-  <si>
-    <t>20040293</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
-  </si>
-  <si>
-    <t>10025848</t>
-  </si>
-  <si>
-    <t>NTRILON 3 RYL VAN400</t>
-  </si>
-  <si>
-    <t>20065095</t>
-  </si>
-  <si>
-    <t>ENSURE/G VANILLA 380</t>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
   </si>
 </sst>
 </file>
@@ -637,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -645,7 +693,7 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -725,24 +773,24 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -759,13 +807,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -782,10 +830,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -802,18 +850,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -822,18 +870,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -842,18 +890,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -862,18 +910,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -882,70 +930,70 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -959,10 +1007,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -970,10 +1018,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -982,7 +1030,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -990,10 +1038,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1002,7 +1050,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1010,19 +1058,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1030,39 +1078,39 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1070,19 +1118,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1090,19 +1138,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1110,19 +1158,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1130,82 +1178,82 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1219,73 +1267,213 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>41</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
